--- a/docs/assets/Wx1_WxC_StudentCredentials.xlsx
+++ b/docs/assets/Wx1_WxC_StudentCredentials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cisco-my.sharepoint.com/personal/vamelend_cisco_com/Documents/Desktop/wbx1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cisco-my.sharepoint.com/personal/vamelend_cisco_com/Documents/Desktop/wbx1/lab/LAB-1251/docs/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8000_{A7B77341-D140-4F02-ACDE-9F5029FB1DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="10_ncr:8000_{A7B77341-D140-4F02-ACDE-9F5029FB1DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9082B66-E6C2-4337-BF7A-0B743679B8DF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30840" yWindow="-120" windowWidth="30960" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Labs Session 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="124">
   <si>
     <t>Student Number</t>
   </si>
@@ -324,230 +324,98 @@
     <t>192.133.193.136</t>
   </si>
   <si>
-    <t>Control Hub Administrator</t>
-  </si>
-  <si>
-    <t>cholland@cb311.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2124!</t>
-  </si>
-  <si>
-    <t>cholland@cb325.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2120!</t>
-  </si>
-  <si>
-    <t>cholland@cb319.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2133!</t>
-  </si>
-  <si>
-    <t>cholland@cb328.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2115!</t>
-  </si>
-  <si>
-    <t>cholland@cb321.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2128!</t>
-  </si>
-  <si>
-    <t>cholland@cb346.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2130!</t>
-  </si>
-  <si>
-    <t>cholland@cb341.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2127!</t>
-  </si>
-  <si>
-    <t>cholland@cb357.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2110!</t>
-  </si>
-  <si>
-    <t>cholland@cb361.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2109!</t>
-  </si>
-  <si>
-    <t>cholland@cb358.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2123!</t>
-  </si>
-  <si>
-    <t>cholland@cb359.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2116!</t>
-  </si>
-  <si>
-    <t>cholland@cb374.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2105!</t>
-  </si>
-  <si>
-    <t>cholland@cb441.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2122!</t>
-  </si>
-  <si>
-    <t>cholland@cb383.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2119!</t>
-  </si>
-  <si>
-    <t>cholland@cb382.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2125!</t>
-  </si>
-  <si>
-    <t>cholland@cb419.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2117!</t>
-  </si>
-  <si>
-    <t>cholland@cb425.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2126!</t>
-  </si>
-  <si>
-    <t>cholland@cb414.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2104!</t>
-  </si>
-  <si>
-    <t>cholland@cb474.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2121!</t>
-  </si>
-  <si>
-    <t>cholland@cb386.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2112!</t>
-  </si>
-  <si>
-    <t>cholland@cb466.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2129!</t>
-  </si>
-  <si>
-    <t>cholland@cb437.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2106!</t>
-  </si>
-  <si>
-    <t>cholland@cb418.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2114!</t>
-  </si>
-  <si>
-    <t>cholland@cb416.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2134!</t>
-  </si>
-  <si>
-    <t>cholland@cb427.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2102!</t>
-  </si>
-  <si>
-    <t>cholland@cb411.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2113!</t>
-  </si>
-  <si>
-    <t>cholland@cb440.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2108!</t>
-  </si>
-  <si>
-    <t>cholland@cb490.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2101!</t>
-  </si>
-  <si>
-    <t>cholland@cb477.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2132!</t>
-  </si>
-  <si>
-    <t>cholland@cb479.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2111!</t>
-  </si>
-  <si>
-    <t>cholland@cb499.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2103!</t>
-  </si>
-  <si>
-    <t>cholland@cb393.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2131!</t>
-  </si>
-  <si>
-    <t>cholland@cb376.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2118!</t>
-  </si>
-  <si>
-    <t>cholland@cb424.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2135!</t>
-  </si>
-  <si>
-    <t>cholland@cb485.dc-05.com</t>
-  </si>
-  <si>
-    <t>dCloud2107!</t>
-  </si>
-  <si>
     <t>Spare</t>
   </si>
   <si>
     <t>Instructor</t>
+  </si>
+  <si>
+    <t>Student Name</t>
+  </si>
+  <si>
+    <t>Control Hub User name</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>cholland@cb348.dc-01.com</t>
+  </si>
+  <si>
+    <t>dCloud9923!</t>
+  </si>
+  <si>
+    <t>Chandra</t>
+  </si>
+  <si>
+    <t>cholland@cb464.dc-01.com</t>
+  </si>
+  <si>
+    <t>dCloud9922!</t>
+  </si>
+  <si>
+    <t>Clayton</t>
+  </si>
+  <si>
+    <t>cholland@cb444.dc-01.com</t>
+  </si>
+  <si>
+    <t>dCloud9921!</t>
+  </si>
+  <si>
+    <t>Kristofer</t>
+  </si>
+  <si>
+    <t>cholland@cb498.dc-01.com</t>
+  </si>
+  <si>
+    <t>dCloud9920!</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>cholland@cb465.dc-01.com</t>
+  </si>
+  <si>
+    <t>dCloud9919!</t>
+  </si>
+  <si>
+    <t>cholland@cb376.dc-01.com</t>
+  </si>
+  <si>
+    <t>dCloud9918!</t>
+  </si>
+  <si>
+    <t>cholland@cb370.dc-01.com</t>
+  </si>
+  <si>
+    <t>dCloud9917!</t>
+  </si>
+  <si>
+    <t>cholland@cb346.dc-01.com</t>
+  </si>
+  <si>
+    <t>dCloud9916!</t>
+  </si>
+  <si>
+    <t>cholland@cb492.dc-01.com</t>
+  </si>
+  <si>
+    <t>dCloud9915!</t>
+  </si>
+  <si>
+    <t>cholland@cb481.dc-01.com</t>
+  </si>
+  <si>
+    <t>dCloud9914!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -696,13 +564,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -892,7 +753,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1073,13 +934,12 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1096,9 +956,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1457,445 +1314,190 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="19.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="3"/>
+      <c r="B2" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="E2" s="2"/>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>99</v>
+      <c r="B3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>101</v>
+      <c r="B4" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>103</v>
+      <c r="B5" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>105</v>
+      <c r="B6" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>107</v>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>109</v>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>111</v>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>113</v>
+      <c r="A10" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>115</v>
+      <c r="A11" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>117</v>
-      </c>
+      <c r="A12"/>
+      <c r="C12"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>119</v>
-      </c>
+      <c r="A13"/>
+      <c r="C13"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>121</v>
-      </c>
+      <c r="A14"/>
+      <c r="C14"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>123</v>
-      </c>
+      <c r="A15"/>
+      <c r="C15"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>125</v>
-      </c>
+      <c r="A16"/>
+      <c r="C16"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>127</v>
-      </c>
+      <c r="A17"/>
+      <c r="C17"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="4">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="4">
-        <v>23</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="4">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="4">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="4">
-        <v>26</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="4">
-        <v>27</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="4">
-        <v>28</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="4">
-        <v>29</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="4">
-        <v>30</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="4">
-        <v>31</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="4">
-        <v>32</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="4">
-        <v>33</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37"/>
-      <c r="C37"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38"/>
-      <c r="C38"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39"/>
-      <c r="C39"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40"/>
-      <c r="C40"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41"/>
-      <c r="C41"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42"/>
-      <c r="C42"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43"/>
+      <c r="A18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B36" r:id="rId1" xr:uid="{473CFBB9-3D42-4F72-A7F2-8E1070D69DF2}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;8&amp;K000000 Cisco Confidential</oddFooter>
@@ -2588,4 +2190,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{c8f49a32-fde3-48a5-9266-b5b0972a22dc}" enabled="1" method="Standard" siteId="{5ae1af62-9505-4097-a69a-c1553ef7840e}" removed="0"/>
+</clbl:labelList>
 </file>